--- a/output/2026-09-01_10_Italia_Liguria_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-01_10_Italia_Liguria_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Attiva dal 1875; verificata su Comune di Genova (P.IVA 03365210107) e PagineGialle</t>
+          <t>Attiva dal 1875; verificata su Comune di Genova (P.IVA 03365210107) e PagineGialle [DUPLICATO — vedi anche: 2026-09-01_00_Italia_Liguria_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Azienda storica (140 anni); catalogo confermato online</t>
+          <t>Azienda storica (140 anni); catalogo confermato online [DUPLICATO — vedi anche: 2026-09-01_00_Italia_Liguria_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -624,7 +624,6 @@
           <t>010 7450222</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Sede legale Genova, stabilimento produttivo a Castenedolo (BS); fornitore utensili</t>
@@ -753,7 +752,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Confermata su sito ufficiale e Facebook; fornisce aziende metalmeccaniche e cantieristica</t>
+          <t>Confermata su sito ufficiale e Facebook; fornisce aziende metalmeccaniche e cantieristica [DUPLICATO — vedi anche: 2026-09-01_00_Italia_Liguria_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -825,7 +824,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>riccardosommovigo@libero.it</t>
@@ -890,7 +888,6 @@
           <t>Euroutensili Service di Ori Adelio</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Ventimiglia (IM)</t>
@@ -906,7 +903,6 @@
           <t>0184 250818</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Telefono reperito su PagineGialle/MisterImprese; nessun sito web proprio</t>
@@ -986,7 +982,6 @@
           <t>019 5090043</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Fondata nel 1997; showroom multi-brand</t>
